--- a/backend/storage/users.xlsx
+++ b/backend/storage/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,44 +441,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ranjithagowda9801@gmail.com</t>
+          <t>sahanashaiva01@gmail.com</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ranju</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>$2b$12$avbGzijLCaq.fzmvpOGSsOrwR5Up87FX/CgZdAq4rhM6LcBfA7H.u</t>
+          <t>$2b$12$7Ihv354Rz9dPF2Rgr1FJJustXQZ42ql6DLxIIg.R7WiI9FflsbmFi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-08T21:27:08.031805</t>
+          <t>2026-05-12T20:56:13.827172</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sahana636407@gmail.com</t>
+          <t>ranjithagowda9801@gmail.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>abc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>$2b$12$Sq9eqWr/GIFAyRnNK67ITeu/4gOMxIJfTuFrknb6sb5cdU3AHltXK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-12T20:57:09.342588</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sahanasahana40163@gmail.com</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>sahana</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>$2b$12$ftFurHIISzeuGuXaIvhZNu43BrOrI54GPJWjsvVrSh9B225jNQwAq</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-08T22:51:19.435355</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>$2b$12$jyGtMnP0sK4ZBKZidJ3Qa.mICjuFGOzLyjYHA4wmvZDbvkqJyc3sa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-13T04:48:32.168406</t>
         </is>
       </c>
     </row>
